--- a/data/final/comexstat/resumo_disponibilidade_comexstat.xlsx
+++ b/data/final/comexstat/resumo_disponibilidade_comexstat.xlsx
@@ -467,10 +467,10 @@
         <v>43861</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -479,7 +479,7 @@
         <v>14429715267</v>
       </c>
       <c r="G2" t="n">
-        <v>33157804370</v>
+        <v>34418070076</v>
       </c>
     </row>
     <row r="3">
@@ -492,10 +492,10 @@
         <v>43861</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -504,7 +504,7 @@
         <v>17190165488</v>
       </c>
       <c r="G3" t="n">
-        <v>25763862100</v>
+        <v>26677510096</v>
       </c>
     </row>
     <row r="4">
@@ -517,10 +517,10 @@
         <v>43861</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>-2760450221</v>
       </c>
       <c r="G4" t="n">
-        <v>7393942270</v>
+        <v>7740559980</v>
       </c>
     </row>
     <row r="5">
@@ -542,10 +542,10 @@
         <v>43861</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
         <v>31619880755</v>
       </c>
       <c r="G5" t="n">
-        <v>58921666470</v>
+        <v>61095580172</v>
       </c>
     </row>
     <row r="6">
@@ -567,10 +567,10 @@
         <v>43861</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D6" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -579,7 +579,7 @@
         <v>46718273016</v>
       </c>
       <c r="G6" t="n">
-        <v>77119199389</v>
+        <v>76342513744</v>
       </c>
     </row>
     <row r="7">
@@ -592,10 +592,10 @@
         <v>43861</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D7" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -604,7 +604,7 @@
         <v>12206525099</v>
       </c>
       <c r="G7" t="n">
-        <v>14073182023</v>
+        <v>14665789542</v>
       </c>
     </row>
     <row r="8">
@@ -617,10 +617,10 @@
         <v>43861</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D8" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -629,7 +629,7 @@
         <v>641249369</v>
       </c>
       <c r="G8" t="n">
-        <v>1548184686</v>
+        <v>1611232587</v>
       </c>
     </row>
     <row r="9">
@@ -642,10 +642,10 @@
         <v>43861</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D9" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -654,7 +654,7 @@
         <v>11309879</v>
       </c>
       <c r="G9" t="n">
-        <v>19241881</v>
+        <v>27463449</v>
       </c>
     </row>
     <row r="10">
@@ -667,10 +667,10 @@
         <v>43861</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D10" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -679,7 +679,7 @@
         <v>17842724736</v>
       </c>
       <c r="G10" t="n">
-        <v>27331288667</v>
+        <v>28316206132</v>
       </c>
     </row>
     <row r="11">
@@ -692,10 +692,10 @@
         <v>43861</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D11" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>395907378</v>
       </c>
       <c r="G11" t="n">
-        <v>753147930</v>
+        <v>809708916</v>
       </c>
     </row>
     <row r="12">
@@ -717,10 +717,10 @@
         <v>43861</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -729,7 +729,7 @@
         <v>1403790404</v>
       </c>
       <c r="G12" t="n">
-        <v>2221291720</v>
+        <v>2306235692</v>
       </c>
     </row>
     <row r="13">
@@ -742,10 +742,10 @@
         <v>43861</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D13" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -754,7 +754,7 @@
         <v>42579</v>
       </c>
       <c r="G13" t="n">
-        <v>170442</v>
+        <v>144681</v>
       </c>
     </row>
     <row r="14">
@@ -767,10 +767,10 @@
         <v>43861</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -779,7 +779,7 @@
         <v>41657</v>
       </c>
       <c r="G14" t="n">
-        <v>143344</v>
+        <v>122543</v>
       </c>
     </row>
     <row r="15">
@@ -792,10 +792,10 @@
         <v>43861</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>357877575</v>
       </c>
       <c r="G15" t="n">
-        <v>1094109253</v>
+        <v>1292800592</v>
       </c>
     </row>
     <row r="16">
@@ -817,10 +817,10 @@
         <v>43861</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D16" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -829,7 +829,7 @@
         <v>163332129</v>
       </c>
       <c r="G16" t="n">
-        <v>206264157</v>
+        <v>235659946</v>
       </c>
     </row>
     <row r="17">
@@ -848,7 +848,7 @@
         <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F17" t="n">
         <v>31418</v>
@@ -873,7 +873,7 @@
         <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F18" t="n">
         <v>20000</v>
@@ -892,10 +892,10 @@
         <v>43861</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D19" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>500185177</v>
       </c>
       <c r="G19" t="n">
-        <v>967242706</v>
+        <v>950751177</v>
       </c>
     </row>
     <row r="20">
@@ -917,10 +917,10 @@
         <v>43861</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D20" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -929,7 +929,7 @@
         <v>103909023</v>
       </c>
       <c r="G20" t="n">
-        <v>162300453</v>
+        <v>156467198</v>
       </c>
     </row>
     <row r="21">
@@ -942,10 +942,10 @@
         <v>43861</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D21" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -954,7 +954,7 @@
         <v>9788257</v>
       </c>
       <c r="G21" t="n">
-        <v>9868969</v>
+        <v>10523613</v>
       </c>
     </row>
     <row r="22">
@@ -967,10 +967,10 @@
         <v>43861</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D22" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -979,7 +979,7 @@
         <v>1182973</v>
       </c>
       <c r="G22" t="n">
-        <v>942383</v>
+        <v>988603</v>
       </c>
     </row>
     <row r="23">
@@ -992,10 +992,10 @@
         <v>43861</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D23" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1004,7 +1004,7 @@
         <v>488810441</v>
       </c>
       <c r="G23" t="n">
-        <v>748163251</v>
+        <v>892280162</v>
       </c>
     </row>
     <row r="24">
@@ -1017,10 +1017,10 @@
         <v>43861</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D24" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1029,7 +1029,7 @@
         <v>1351894846</v>
       </c>
       <c r="G24" t="n">
-        <v>1412673002</v>
+        <v>1801287673</v>
       </c>
     </row>
     <row r="25">
@@ -1042,10 +1042,10 @@
         <v>43861</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D25" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E25" t="n">
         <v>10</v>
@@ -1054,7 +1054,7 @@
         <v>23393</v>
       </c>
       <c r="G25" t="n">
-        <v>1381516</v>
+        <v>1255725</v>
       </c>
     </row>
     <row r="26">
@@ -1067,10 +1067,10 @@
         <v>43861</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D26" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E26" t="n">
         <v>10</v>
@@ -1079,7 +1079,7 @@
         <v>40720</v>
       </c>
       <c r="G26" t="n">
-        <v>1452782</v>
+        <v>1333748</v>
       </c>
     </row>
     <row r="27">
@@ -1092,10 +1092,10 @@
         <v>43861</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D27" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1104,7 +1104,7 @@
         <v>401663716</v>
       </c>
       <c r="G27" t="n">
-        <v>893582419</v>
+        <v>649437972</v>
       </c>
     </row>
     <row r="28">
@@ -1117,10 +1117,10 @@
         <v>43861</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D28" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1129,7 +1129,7 @@
         <v>955961547</v>
       </c>
       <c r="G28" t="n">
-        <v>1438094595</v>
+        <v>942054629</v>
       </c>
     </row>
     <row r="29">
@@ -1148,7 +1148,7 @@
         <v>43</v>
       </c>
       <c r="E29" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F29" t="n">
         <v>13124930</v>
@@ -1173,7 +1173,7 @@
         <v>43</v>
       </c>
       <c r="E30" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F30" t="n">
         <v>40054409</v>
@@ -1192,10 +1192,10 @@
         <v>43861</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D31" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1204,7 +1204,7 @@
         <v>349915062</v>
       </c>
       <c r="G31" t="n">
-        <v>1002656682</v>
+        <v>1228786726</v>
       </c>
     </row>
     <row r="32">
@@ -1217,10 +1217,10 @@
         <v>43861</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D32" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -1229,7 +1229,7 @@
         <v>2083530104</v>
       </c>
       <c r="G32" t="n">
-        <v>4653100189</v>
+        <v>5207728793</v>
       </c>
     </row>
     <row r="33">
@@ -1242,10 +1242,10 @@
         <v>43861</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D33" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -1254,7 +1254,7 @@
         <v>26216991</v>
       </c>
       <c r="G33" t="n">
-        <v>33273820</v>
+        <v>37058160</v>
       </c>
     </row>
     <row r="34">
@@ -1267,10 +1267,10 @@
         <v>43861</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D34" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>196178640</v>
       </c>
       <c r="G34" t="n">
-        <v>199281400</v>
+        <v>220704294</v>
       </c>
     </row>
     <row r="35">
@@ -1292,10 +1292,10 @@
         <v>43861</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D35" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -1304,7 +1304,7 @@
         <v>1627139024</v>
       </c>
       <c r="G35" t="n">
-        <v>2051566400</v>
+        <v>1771842975</v>
       </c>
     </row>
     <row r="36">
@@ -1317,10 +1317,10 @@
         <v>43861</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D36" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -1329,7 +1329,7 @@
         <v>25418986258</v>
       </c>
       <c r="G36" t="n">
-        <v>34406447895</v>
+        <v>31660490297</v>
       </c>
     </row>
     <row r="37">
@@ -1342,10 +1342,10 @@
         <v>43861</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D37" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E37" t="n">
         <v>14</v>
@@ -1354,7 +1354,7 @@
         <v>6207</v>
       </c>
       <c r="G37" t="n">
-        <v>6950029</v>
+        <v>5139747</v>
       </c>
     </row>
     <row r="38">
@@ -1367,10 +1367,10 @@
         <v>43861</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D38" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E38" t="n">
         <v>14</v>
@@ -1379,7 +1379,7 @@
         <v>7200</v>
       </c>
       <c r="G38" t="n">
-        <v>78331372</v>
+        <v>61011592</v>
       </c>
     </row>
     <row r="39">
@@ -1392,10 +1392,10 @@
         <v>43861</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D39" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -1404,7 +1404,7 @@
         <v>1707992437</v>
       </c>
       <c r="G39" t="n">
-        <v>4828191084</v>
+        <v>6498868606</v>
       </c>
     </row>
     <row r="40">
@@ -1417,10 +1417,10 @@
         <v>43861</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D40" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -1429,7 +1429,7 @@
         <v>4221906804</v>
       </c>
       <c r="G40" t="n">
-        <v>8379911835</v>
+        <v>11689652591</v>
       </c>
     </row>
     <row r="41">
@@ -1442,10 +1442,10 @@
         <v>43861</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D41" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -1454,7 +1454,7 @@
         <v>207990371</v>
       </c>
       <c r="G41" t="n">
-        <v>547298813</v>
+        <v>631617247</v>
       </c>
     </row>
     <row r="42">
@@ -1467,10 +1467,10 @@
         <v>43861</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D42" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -1479,7 +1479,7 @@
         <v>432290309</v>
       </c>
       <c r="G42" t="n">
-        <v>797225701</v>
+        <v>893774707</v>
       </c>
     </row>
     <row r="43">
@@ -1492,10 +1492,10 @@
         <v>43861</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D43" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -1504,7 +1504,7 @@
         <v>281324952</v>
       </c>
       <c r="G43" t="n">
-        <v>646488066</v>
+        <v>755950210</v>
       </c>
     </row>
     <row r="44">
@@ -1517,10 +1517,10 @@
         <v>43861</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D44" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>831821378</v>
       </c>
       <c r="G44" t="n">
-        <v>1790486389</v>
+        <v>1941525390</v>
       </c>
     </row>
     <row r="45">
@@ -1548,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F45" t="n">
         <v>2282</v>
@@ -1573,7 +1573,7 @@
         <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F46" t="n">
         <v>2500</v>
@@ -1592,10 +1592,10 @@
         <v>43861</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D47" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -1604,7 +1604,7 @@
         <v>504774218</v>
       </c>
       <c r="G47" t="n">
-        <v>4410039153</v>
+        <v>3473089697</v>
       </c>
     </row>
     <row r="48">
@@ -1617,10 +1617,10 @@
         <v>43861</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D48" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -1629,7 +1629,7 @@
         <v>1397018249</v>
       </c>
       <c r="G48" t="n">
-        <v>9808807495</v>
+        <v>7358383641</v>
       </c>
     </row>
     <row r="49">
@@ -1642,10 +1642,10 @@
         <v>43861</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D49" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E49" t="n">
         <v>4</v>
@@ -1654,7 +1654,7 @@
         <v>6305340</v>
       </c>
       <c r="G49" t="n">
-        <v>44621019</v>
+        <v>51965570</v>
       </c>
     </row>
     <row r="50">
@@ -1667,10 +1667,10 @@
         <v>43861</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="D50" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E50" t="n">
         <v>4</v>
@@ -1679,7 +1679,7 @@
         <v>19690000</v>
       </c>
       <c r="G50" t="n">
-        <v>109088024</v>
+        <v>117130000</v>
       </c>
     </row>
   </sheetData>
